--- a/data/Example_Schedule.xlsx
+++ b/data/Example_Schedule.xlsx
@@ -60,7 +60,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -97,11 +97,25 @@
         <color rgb="00B7B7B7"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00FFFFFF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00FFFFFF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00FFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00FFFFFF"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -110,6 +124,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -477,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27.85546875" customWidth="1" min="1" max="1"/>
@@ -553,18 +570,6 @@
       <c r="B6" t="inlineStr">
         <is>
           <t>parquet</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>loadstep_seconds</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>30</t>
         </is>
       </c>
     </row>
@@ -693,7 +698,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -704,52 +709,42 @@
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>step_id</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>enabled</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>actions</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="E1" s="4" t="inlineStr">
         <is>
           <t>wait</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
-        <is>
-          <t>continuous</t>
-        </is>
-      </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="F1" s="4" t="inlineStr">
         <is>
           <t>take_loadstep</t>
         </is>
       </c>
-      <c r="H1" s="3" t="inlineStr">
-        <is>
-          <t>loadstep_name</t>
-        </is>
-      </c>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
       <c r="I1" s="2" t="n"/>
       <c r="J1" s="2" t="n"/>
       <c r="K1" s="2" t="n"/>
       <c r="L1" s="2" t="n"/>
-      <c r="M1" s="2" t="n"/>
-      <c r="N1" s="2" t="n"/>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -787,7 +782,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -798,52 +793,42 @@
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>step_id</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>enabled</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>actions</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="E1" s="4" t="inlineStr">
         <is>
           <t>wait</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
-        <is>
-          <t>continuous</t>
-        </is>
-      </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="F1" s="4" t="inlineStr">
         <is>
           <t>take_loadstep</t>
         </is>
       </c>
-      <c r="H1" s="3" t="inlineStr">
-        <is>
-          <t>loadstep_name</t>
-        </is>
-      </c>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
       <c r="I1" s="2" t="n"/>
       <c r="J1" s="2" t="n"/>
       <c r="K1" s="2" t="n"/>
       <c r="L1" s="2" t="n"/>
-      <c r="M1" s="2" t="n"/>
-      <c r="N1" s="2" t="n"/>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">

--- a/data/Example_Schedule.xlsx
+++ b/data/Example_Schedule.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27.85546875" customWidth="1" min="1" max="1"/>
@@ -570,6 +570,18 @@
       <c r="B6" t="inlineStr">
         <is>
           <t>parquet</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>loadstep_duration_seconds</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>45</t>
         </is>
       </c>
     </row>
@@ -904,6 +916,11 @@
           <t>any(cond:brewcan.density.0:&lt;=:1.040:60;elapsed:900)</t>
         </is>
       </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>rising(any(cond:brewcan.density.0:&lt;=:1.040;cond:pressure:&gt;=:0.8))</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -954,6 +971,11 @@
           <t>any(cond:brewcan.density.0:&lt;=:1.018:120;elapsed:900)</t>
         </is>
       </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>falling(cond:set_allow_Gas:==:1)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1002,6 +1024,11 @@
       <c r="E8" t="inlineStr">
         <is>
           <t>all(elapsed:1200;cond:temp:&lt;=:14.1:120)</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>pulse(cond:temp:&lt;=:5;30)</t>
         </is>
       </c>
     </row>
